--- a/ejemplo/Ejemplo_MEP.xlsx
+++ b/ejemplo/Ejemplo_MEP.xlsx
@@ -43,45 +43,75 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tamaño MEP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Longitud (m)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área (m²)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Área bruta (m²)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Volumen (m³)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Altura</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Anchura</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Diámetro</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espesor del aislamiento</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">Longitud</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tamaño</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t xml:space="preserve">Área</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Coste</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Código de montaje</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Descripción de montaje</t>
         </is>
@@ -118,32 +148,40 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
+        </is>
+      </c>
+      <c r="H2">
+        <v>18.0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">28,0 mm</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18,00 m</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -180,32 +218,40 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 mmø</t>
+        </is>
+      </c>
+      <c r="H3">
+        <v>12.0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">22,0 mm</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12,00 m</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="P3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.000 mm</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t xml:space="preserve">22 mmø</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -242,32 +288,40 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 mmø</t>
+        </is>
+      </c>
+      <c r="H4">
+        <v>6.0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">15,0 mm</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6,00 m</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.000 mm</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t xml:space="preserve">15 mmø</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -304,7 +358,12 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø-28 mmø</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø-28 mmø</t>
         </is>
@@ -341,7 +400,12 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 mmø-22 mmø</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t xml:space="preserve">22 mmø-22 mmø</t>
         </is>
@@ -360,17 +424,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductos</t>
+          <t xml:space="preserve">Aislamientos de tuberías</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducto rectangular</t>
+          <t xml:space="preserve">Aislamiento de tuberías</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapa galvanizada</t>
+          <t xml:space="preserve">Coquilla elastomérica</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -380,27 +444,25 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400 mm</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16,00 m</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400x300</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22,40 m²</t>
+          <t xml:space="preserve">19 mm</t>
+        </is>
+      </c>
+      <c r="H7">
+        <v>18.0</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 mm</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
         </is>
       </c>
     </row>
@@ -417,17 +479,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductos</t>
+          <t xml:space="preserve">Aislamientos de tuberías</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducto rectangular</t>
+          <t xml:space="preserve">Aislamiento de tuberías</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapa galvanizada</t>
+          <t xml:space="preserve">Coquilla elastomérica</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -437,27 +499,25 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">200 mm</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9,00 m</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300x200</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9,00 m²</t>
+          <t xml:space="preserve">13 mm</t>
+        </is>
+      </c>
+      <c r="H8">
+        <v>12.0</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 mm</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.000 mm</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
         </is>
       </c>
     </row>
@@ -474,17 +534,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bandejas de cables</t>
+          <t xml:space="preserve">Conductos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bandeja de cables con uniones</t>
+          <t xml:space="preserve">Conducto rectangular</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rejilla</t>
+          <t xml:space="preserve">Chapa galvanizada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -492,14 +552,40 @@
           <t xml:space="preserve">Planta baja</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18,00 m</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mmx60 mm</t>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400x300</t>
+        </is>
+      </c>
+      <c r="H9">
+        <v>16.0</v>
+      </c>
+      <c r="I9">
+        <v>22.4</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400 mm</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16,00 m</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400x300</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22,40 m²</t>
         </is>
       </c>
     </row>
@@ -516,52 +602,58 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Conductos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Conducto rectangular</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cobre</t>
+          <t xml:space="preserve">Chapa galvanizada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planta 1</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28,0 mm</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18,00 m</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28 mmø</t>
+          <t xml:space="preserve">Planta baja</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300x200</t>
+        </is>
+      </c>
+      <c r="H10">
+        <v>9.0</v>
+      </c>
+      <c r="I10">
+        <v>9.0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200 mm</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t xml:space="preserve">18,50</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D2020</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Distribución de agua</t>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9,00 m</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300x200</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9,00 m²</t>
         </is>
       </c>
     </row>
@@ -578,52 +670,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Bandejas de cables</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Bandeja de cables con uniones</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cobre</t>
+          <t xml:space="preserve">Rejilla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planta 1</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22,0 mm</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12,00 m</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 mmø</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18,50</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D2020</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Distribución de agua</t>
+          <t xml:space="preserve">Planta baja</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mmx60 mm</t>
+        </is>
+      </c>
+      <c r="H11">
+        <v>18.0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mmx60 mm</t>
         </is>
       </c>
     </row>
@@ -658,32 +738,40 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15,0 mm</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6,00 m</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 mmø</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
+        </is>
+      </c>
+      <c r="H12">
+        <v>18.0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28,0 mm</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -702,17 +790,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accesorios de tuberías</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codo - Cobre</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estándar</t>
+          <t xml:space="preserve">Cobre</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -720,9 +808,42 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28 mmø-28 mmø</t>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 mmø</t>
+        </is>
+      </c>
+      <c r="H13">
+        <v>12.0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22,0 mm</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.000 mm</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 mmø</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18,50</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D2020</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distribución de agua</t>
         </is>
       </c>
     </row>
@@ -739,17 +860,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accesorios de tuberías</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codo - Cobre</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estándar</t>
+          <t xml:space="preserve">Cobre</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -757,9 +878,42 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 mmø-22 mmø</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 mmø</t>
+        </is>
+      </c>
+      <c r="H14">
+        <v>6.0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15,0 mm</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.000 mm</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 mmø</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18,50</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D2020</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distribución de agua</t>
         </is>
       </c>
     </row>
@@ -776,17 +930,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductos</t>
+          <t xml:space="preserve">Accesorios de tuberías</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducto rectangular</t>
+          <t xml:space="preserve">Codo - Cobre</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapa galvanizada</t>
+          <t xml:space="preserve">Estándar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -796,27 +950,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400 mm</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16,00 m</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400x300</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22,40 m²</t>
+          <t xml:space="preserve">28 mmø-28 mmø</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø-28 mmø</t>
         </is>
       </c>
     </row>
@@ -833,17 +972,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductos</t>
+          <t xml:space="preserve">Accesorios de tuberías</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducto rectangular</t>
+          <t xml:space="preserve">Codo - Cobre</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapa galvanizada</t>
+          <t xml:space="preserve">Estándar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -853,27 +992,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">200 mm</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9,00 m</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300x200</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9,00 m²</t>
+          <t xml:space="preserve">22 mmø-22 mmø</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 mmø-22 mmø</t>
         </is>
       </c>
     </row>
@@ -890,17 +1014,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bandejas de cables</t>
+          <t xml:space="preserve">Aislamientos de tuberías</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bandeja de cables con uniones</t>
+          <t xml:space="preserve">Aislamiento de tuberías</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rejilla</t>
+          <t xml:space="preserve">Coquilla elastomérica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -908,14 +1032,27 @@
           <t xml:space="preserve">Planta 1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18,00 m</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mmx60 mm</t>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 mm</t>
+        </is>
+      </c>
+      <c r="H17">
+        <v>18.0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 mm</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
         </is>
       </c>
     </row>
@@ -932,52 +1069,45 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Aislamientos de tuberías</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Aislamiento de tuberías</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cobre</t>
+          <t xml:space="preserve">Coquilla elastomérica</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planta 2</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28,0 mm</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18,00 m</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
+          <t xml:space="preserve">Planta 1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 mm</t>
+        </is>
+      </c>
+      <c r="H18">
+        <v>12.0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 mm</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.000 mm</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18,50</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D2020</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Distribución de agua</t>
         </is>
       </c>
     </row>
@@ -994,52 +1124,58 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Conductos</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Conducto rectangular</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cobre</t>
+          <t xml:space="preserve">Chapa galvanizada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planta 2</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22,0 mm</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12,00 m</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 mmø</t>
+          <t xml:space="preserve">Planta 1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400x300</t>
+        </is>
+      </c>
+      <c r="H19">
+        <v>16.0</v>
+      </c>
+      <c r="I19">
+        <v>22.4</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">18,50</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D2020</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Distribución de agua</t>
+          <t xml:space="preserve">400 mm</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16,00 m</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400x300</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22,40 m²</t>
         </is>
       </c>
     </row>
@@ -1056,52 +1192,58 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Conductos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tuberías</t>
+          <t xml:space="preserve">Conducto rectangular</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cobre</t>
+          <t xml:space="preserve">Chapa galvanizada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planta 2</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15,0 mm</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6,00 m</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 mmø</t>
+          <t xml:space="preserve">Planta 1</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300x200</t>
+        </is>
+      </c>
+      <c r="H20">
+        <v>9.0</v>
+      </c>
+      <c r="I20">
+        <v>9.0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200 mm</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">18,50</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D2020</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Distribución de agua</t>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9,00 m</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300x200</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9,00 m²</t>
         </is>
       </c>
     </row>
@@ -1118,27 +1260,40 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accesorios de tuberías</t>
+          <t xml:space="preserve">Bandejas de cables</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codo - Cobre</t>
+          <t xml:space="preserve">Bandeja de cables con uniones</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estándar</t>
+          <t xml:space="preserve">Rejilla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Planta 2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28 mmø-28 mmø</t>
+          <t xml:space="preserve">Planta 1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mmx60 mm</t>
+        </is>
+      </c>
+      <c r="H21">
+        <v>18.0</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mmx60 mm</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1310,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accesorios de tuberías</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codo - Cobre</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Estándar</t>
+          <t xml:space="preserve">Cobre</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1173,9 +1328,42 @@
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22 mmø-22 mmø</t>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
+        </is>
+      </c>
+      <c r="H22">
+        <v>18.0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28,0 mm</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18,50</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D2020</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distribución de agua</t>
         </is>
       </c>
     </row>
@@ -1192,17 +1380,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductos</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducto rectangular</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapa galvanizada</t>
+          <t xml:space="preserve">Cobre</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1212,27 +1400,40 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400 mm</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16,00 m</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">400x300</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22,40 m²</t>
+          <t xml:space="preserve">22 mmø</t>
+        </is>
+      </c>
+      <c r="H23">
+        <v>12.0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22,0 mm</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.000 mm</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 mmø</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18,50</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D2020</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distribución de agua</t>
         </is>
       </c>
     </row>
@@ -1249,17 +1450,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conductos</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducto rectangular</t>
+          <t xml:space="preserve">Tuberías</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chapa galvanizada</t>
+          <t xml:space="preserve">Cobre</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1269,27 +1470,40 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">200 mm</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300 mm</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9,00 m</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300x200</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9,00 m²</t>
+          <t xml:space="preserve">15 mmø</t>
+        </is>
+      </c>
+      <c r="H24">
+        <v>6.0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15,0 mm</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.000 mm</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15 mmø</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18,50</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D2020</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distribución de agua</t>
         </is>
       </c>
     </row>
@@ -1306,30 +1520,368 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Accesorios de tuberías</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codo - Cobre</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estándar</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø-28 mmø</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø-28 mmø</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520075</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0007ef8b-0000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accesorios de tuberías</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Codo - Cobre</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estándar</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 mmø-22 mmø</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22 mmø-22 mmø</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520078</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0007ef8e-0000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aislamientos de tuberías</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aislamiento de tuberías</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coquilla elastomérica</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 mm</t>
+        </is>
+      </c>
+      <c r="H27">
+        <v>18.0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 mm</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520081</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0007ef91-0000</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aislamientos de tuberías</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aislamiento de tuberías</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coquilla elastomérica</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 mm</t>
+        </is>
+      </c>
+      <c r="H28">
+        <v>12.0</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 mm</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12.000 mm</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28 mmø</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520084</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0007ef94-0000</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductos</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conducto rectangular</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chapa galvanizada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400x300</t>
+        </is>
+      </c>
+      <c r="H29">
+        <v>16.0</v>
+      </c>
+      <c r="I29">
+        <v>22.4</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400 mm</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16,00 m</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">400x300</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22,40 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520087</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0007ef97-0000</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conductos</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conducto rectangular</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chapa galvanizada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Planta 2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300x200</t>
+        </is>
+      </c>
+      <c r="H30">
+        <v>9.0</v>
+      </c>
+      <c r="I30">
+        <v>9.0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200 mm</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mm</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9,00 m</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300x200</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9,00 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">520090</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5e2a0007ef9a-0000</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bandejas de cables</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t xml:space="preserve">Bandeja de cables con uniones</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">Rejilla</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t xml:space="preserve">Planta 2</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18,00 m</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300 mmx60 mm</t>
+        </is>
+      </c>
+      <c r="H31">
+        <v>18.0</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18.000 mm</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mmx60 mm</t>
         </is>

--- a/ejemplo/Ejemplo_MEP.xlsx
+++ b/ejemplo/Ejemplo_MEP.xlsx
@@ -68,50 +68,60 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t xml:space="preserve">W (kg/m)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Peso (kg)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Altura</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Anchura</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t xml:space="preserve">Diámetro</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t xml:space="preserve">Espesor del aislamiento</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t xml:space="preserve">Longitud</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tamaño</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t xml:space="preserve">Área</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Coste</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Código de montaje</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tipo: Descripción de montaje</t>
         </is>
@@ -156,32 +166,32 @@
       <c r="H2">
         <v>18.0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t xml:space="preserve">28,0 mm</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -226,32 +236,32 @@
       <c r="H3">
         <v>12.0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t xml:space="preserve">22,0 mm</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t xml:space="preserve">12.000 mm</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t xml:space="preserve">22 mmø</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -296,32 +306,32 @@
       <c r="H4">
         <v>6.0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t xml:space="preserve">15,0 mm</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t xml:space="preserve">6.000 mm</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t xml:space="preserve">15 mmø</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -363,7 +373,7 @@
           <t xml:space="preserve">28 mmø-28 mmø</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø-28 mmø</t>
         </is>
@@ -405,7 +415,7 @@
           <t xml:space="preserve">22 mmø-22 mmø</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t xml:space="preserve">22 mmø-22 mmø</t>
         </is>
@@ -450,17 +460,17 @@
       <c r="H7">
         <v>18.0</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t xml:space="preserve">19 mm</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
@@ -505,17 +515,17 @@
       <c r="H8">
         <v>12.0</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t xml:space="preserve">13 mm</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t xml:space="preserve">12.000 mm</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
@@ -563,27 +573,27 @@
       <c r="I9">
         <v>22.4</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">400 mm</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t xml:space="preserve">16,00 m</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t xml:space="preserve">400x300</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t xml:space="preserve">22,40 m²</t>
         </is>
@@ -631,27 +641,27 @@
       <c r="I10">
         <v>9.0</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">200 mm</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t xml:space="preserve">9,00 m</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t xml:space="preserve">300x200</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t xml:space="preserve">9,00 m²</t>
         </is>
@@ -696,12 +706,12 @@
       <c r="H11">
         <v>18.0</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mmx60 mm</t>
         </is>
@@ -746,32 +756,32 @@
       <c r="H12">
         <v>18.0</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t xml:space="preserve">28,0 mm</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -816,32 +826,32 @@
       <c r="H13">
         <v>12.0</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t xml:space="preserve">22,0 mm</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t xml:space="preserve">12.000 mm</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t xml:space="preserve">22 mmø</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -886,32 +896,32 @@
       <c r="H14">
         <v>6.0</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t xml:space="preserve">15,0 mm</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t xml:space="preserve">6.000 mm</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t xml:space="preserve">15 mmø</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -953,7 +963,7 @@
           <t xml:space="preserve">28 mmø-28 mmø</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø-28 mmø</t>
         </is>
@@ -995,7 +1005,7 @@
           <t xml:space="preserve">22 mmø-22 mmø</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t xml:space="preserve">22 mmø-22 mmø</t>
         </is>
@@ -1040,17 +1050,17 @@
       <c r="H17">
         <v>18.0</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t xml:space="preserve">19 mm</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
@@ -1095,17 +1105,17 @@
       <c r="H18">
         <v>12.0</v>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t xml:space="preserve">13 mm</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t xml:space="preserve">12.000 mm</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
@@ -1153,27 +1163,27 @@
       <c r="I19">
         <v>22.4</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">400 mm</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t xml:space="preserve">16,00 m</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t xml:space="preserve">400x300</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t xml:space="preserve">22,40 m²</t>
         </is>
@@ -1221,27 +1231,27 @@
       <c r="I20">
         <v>9.0</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t xml:space="preserve">200 mm</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t xml:space="preserve">9,00 m</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t xml:space="preserve">300x200</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t xml:space="preserve">9,00 m²</t>
         </is>
@@ -1286,12 +1296,12 @@
       <c r="H21">
         <v>18.0</v>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mmx60 mm</t>
         </is>
@@ -1336,32 +1346,32 @@
       <c r="H22">
         <v>18.0</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t xml:space="preserve">28,0 mm</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -1406,32 +1416,32 @@
       <c r="H23">
         <v>12.0</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t xml:space="preserve">22,0 mm</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t xml:space="preserve">12.000 mm</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t xml:space="preserve">22 mmø</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -1476,32 +1486,32 @@
       <c r="H24">
         <v>6.0</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t xml:space="preserve">15,0 mm</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t xml:space="preserve">6.000 mm</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t xml:space="preserve">15 mmø</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t xml:space="preserve">18,50</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t xml:space="preserve">D2020</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t xml:space="preserve">Distribución de agua</t>
         </is>
@@ -1543,7 +1553,7 @@
           <t xml:space="preserve">28 mmø-28 mmø</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø-28 mmø</t>
         </is>
@@ -1585,7 +1595,7 @@
           <t xml:space="preserve">22 mmø-22 mmø</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t xml:space="preserve">22 mmø-22 mmø</t>
         </is>
@@ -1630,17 +1640,17 @@
       <c r="H27">
         <v>18.0</v>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t xml:space="preserve">19 mm</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
@@ -1685,17 +1695,17 @@
       <c r="H28">
         <v>12.0</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t xml:space="preserve">13 mm</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t xml:space="preserve">12.000 mm</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t xml:space="preserve">28 mmø</t>
         </is>
@@ -1743,27 +1753,27 @@
       <c r="I29">
         <v>22.4</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">400 mm</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t xml:space="preserve">16,00 m</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t xml:space="preserve">400x300</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t xml:space="preserve">22,40 m²</t>
         </is>
@@ -1811,27 +1821,27 @@
       <c r="I30">
         <v>9.0</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">200 mm</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mm</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t xml:space="preserve">9,00 m</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t xml:space="preserve">300x200</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t xml:space="preserve">9,00 m²</t>
         </is>
@@ -1876,12 +1886,12 @@
       <c r="H31">
         <v>18.0</v>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t xml:space="preserve">18.000 mm</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t xml:space="preserve">300 mmx60 mm</t>
         </is>
